--- a/artfynd/A 25179-2023 artfynd.xlsx
+++ b/artfynd/A 25179-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25179-2023 artfynd.xlsx
+++ b/artfynd/A 25179-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56196521</v>
+        <v>56220923</v>
       </c>
       <c r="B2" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1968</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>678877.0723790007</v>
+        <v>678872</v>
       </c>
       <c r="R2" t="n">
-        <v>6684810.108405312</v>
+        <v>6684810</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,24 +752,14 @@
           <t>2004-08-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2004-08-27</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1 ex. under äldre gran och tall. Hatt 8 cm bred, utbredd, grårosa. Fot 9 cm hög, 2 cm tjock, med avsmalnande bas. Foten är grårosa upptill och blir mörkt purpurbrun vid basen. Kött ljust med rosa ton. Lukt som av buljongtärning. Smak mild. Sporpulver rent vitt. Sporer nästan klotrunda, fint taggiga, 4-5 μm.</t>
+          <t>3 ex. under äldre gran och tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,6 +788,471 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>69563989</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90663</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ytternuttö 5 km NNO om Hökhuvud kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>678901</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6684797</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2006-09-20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2006-09-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ca. 50 ex. under medelåldrig tall på gammal åkermark.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Medelåldrig barrskog på gammal åkermark.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>56196521</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93231</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1968</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grantaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellodon violascens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ytternuttö 5 km NNO om Hökhuvud kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>678877</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6684810</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2004-08-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2004-08-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 ex. under äldre gran och tall. Hatt 8 cm bred, utbredd, grårosa. Fot 9 cm hög, 2 cm tjock, med avsmalnande bas. Foten är grårosa upptill och blir mörkt purpurbrun vid basen. Kött ljust med rosa ton. Lukt som av buljongtärning. Smak mild. Sporpulver rent vitt. Sporer nästan klotrunda, fint taggiga, 4-5 μm.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre, mossrik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>69529633</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ytternuttö 5 km NNO om Hökhuvud kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>678857</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6684795</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2004-08-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2004-08-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca. 10 ex.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>60780780</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93200</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6003297</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spricktaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum glaucopus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ytternuttö 5 km NNO om Hökhuvud kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>678829</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6684822</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2006-09-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2006-09-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>4 ex. i mossvegetation intill en stig, i äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25179-2023 artfynd.xlsx
+++ b/artfynd/A 25179-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220923</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69563989</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56196521</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69529633</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,8 +1278,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60780780</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>